--- a/resultados/third_review/20260907_data2024_medication_spending.xlsx
+++ b/resultados/third_review/20260907_data2024_medication_spending.xlsx
@@ -41,25 +41,25 @@
     <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE</t>
   </si>
   <si>
+    <t xml:space="preserve">OCTREOTIDE 0.1 MG/ML INJECTABLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">CABERGOLINE 0.5 MG</t>
   </si>
   <si>
+    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANREOTIDE 60 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANREOTIDE 90 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCTREOTIDE LAR 20 MG INJECTABLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">OCTREOTIDE LAR 30 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCTREOTIDE 0.1 MG/ML INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANREOTIDE 60 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANREOTIDE 90 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCTREOTIDE LAR 20 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -422,25 +422,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>613</v>
+        <v>567</v>
       </c>
       <c r="C2" t="n">
-        <v>1125124.42</v>
+        <v>1366050.42</v>
       </c>
       <c r="D2" t="n">
-        <v>1835.44</v>
+        <v>2409.26</v>
       </c>
       <c r="E2" t="n">
-        <v>612</v>
+        <v>566</v>
       </c>
       <c r="F2" t="n">
-        <v>1122715.16</v>
+        <v>1363641.16</v>
       </c>
       <c r="G2" t="n">
-        <v>1834.5</v>
+        <v>2409.26</v>
       </c>
       <c r="H2" t="n">
-        <v>1122715.16</v>
+        <v>1363641.16</v>
       </c>
     </row>
     <row r="3">
@@ -448,25 +448,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>189100</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>233698.22</v>
+        <v>375.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1.24</v>
+        <v>28.9</v>
       </c>
       <c r="E3" t="n">
-        <v>188302</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>233698.22</v>
+        <v>375.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.24</v>
+        <v>28.9</v>
       </c>
       <c r="H3" t="n">
-        <v>233698.22</v>
+        <v>375.7</v>
       </c>
     </row>
     <row r="4">
@@ -474,25 +474,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>19330</v>
+        <v>224510</v>
       </c>
       <c r="C4" t="n">
-        <v>7227.78</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>19311</v>
+        <v>223722</v>
       </c>
       <c r="F4" t="n">
-        <v>7227.78</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7227.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -500,25 +500,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>7018</v>
       </c>
       <c r="C5" t="n">
-        <v>375.7</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>6999</v>
       </c>
       <c r="F5" t="n">
-        <v>375.7</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>375.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -526,7 +526,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>24568</v>
+        <v>290</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>24549</v>
+        <v>289</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -552,7 +552,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>526</v>
+        <v>1998</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>525</v>
+        <v>1993</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -578,7 +578,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>3184</v>
+        <v>6804</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -587,7 +587,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3180</v>
+        <v>6769</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>11700</v>
+        <v>7834</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>11671</v>
+        <v>7812</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
